--- a/frontend/src/assets/Template.xlsx
+++ b/frontend/src/assets/Template.xlsx
@@ -27,7 +27,7 @@
     <comment ref="H2" authorId="0">
       <text>
         <r>
-          <t>Comma-separated scheme names, e.g. "AMRUT 1.0, Namami Gange".</t>
+          <t>Pick from the Schemes sheet.</t>
         </r>
       </text>
     </comment>
@@ -145,7 +145,7 @@
     <t>CoS/EoT events, GeoTagging photos, and Management Action items each belong to a project but are entered from the Input Sheet directly after the project exists — the "…Log" sheets here are blank reference templates for jotting that data down by hand, not something this import reads.</t>
   </si>
   <si>
-    <t>Generated: 2026-09-02 11:46:57Z</t>
+    <t>Generated: 2026-10-03 10:09:27Z</t>
   </si>
   <si>
     <t>#</t>
@@ -1946,7 +1946,7 @@
         <v>98</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="N3" s="16" t="s">
         <v>103</v>
@@ -3128,7 +3128,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:BT2"/>
-  <dataValidations count="42">
+  <dataValidations count="44">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="AA4:AA203">
       <formula1>0</formula1>
     </dataValidation>
@@ -3224,8 +3224,14 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick a name from the Divisions sheet." sqref="E4:E203">
       <formula1>=Divisions!$A$2:$A$46</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick a name from the Schemes sheet." sqref="H4:H203">
+      <formula1>=Schemes!$A$2:$A$9</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: Work Contract, Service Contract, O&amp;M Contract, Others" sqref="K4:K203">
       <formula1>"Work Contract,Service Contract,O&amp;M Contract,Others"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: BUIDCo" sqref="M4:M203">
+      <formula1>"BUIDCo"</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="N4:N203">
       <formula1>32874</formula1>
@@ -3315,6 +3321,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: Scope Addition, Scope Deletion, Design Change, Quantity Variation, Others" sqref="D2:D201">
+      <formula1>"Scope Addition,Scope Deletion,Design Change,Quantity Variation,Others"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3373,6 +3384,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: Open, Closed" sqref="C2:C201">
+      <formula1>"Open,Closed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/frontend/src/assets/Template.xlsx
+++ b/frontend/src/assets/Template.xlsx
@@ -52,35 +52,35 @@
         </r>
       </text>
     </comment>
-    <comment ref="BE2" authorId="0">
+    <comment ref="BJ2" authorId="0">
       <text>
         <r>
           <t>Full https:// URL. Site photos are added from the Input Sheet directly (upload or link) — see the GeoTagging Photos Log sheet.</t>
         </r>
       </text>
     </comment>
-    <comment ref="BG2" authorId="0">
+    <comment ref="BL2" authorId="0">
       <text>
         <r>
           <t>Fill only if there is an outstanding gap; blank means "no gap".</t>
         </r>
       </text>
     </comment>
-    <comment ref="BK2" authorId="0">
+    <comment ref="BP2" authorId="0">
       <text>
         <r>
           <t>Leave blank to auto-calculate from Start Date + Period.</t>
         </r>
       </text>
     </comment>
-    <comment ref="BS2" authorId="0">
+    <comment ref="BX2" authorId="0">
       <text>
         <r>
           <t>Only when Funding Source = "Central - State Share". Central % + State % must not exceed 100.</t>
         </r>
       </text>
     </comment>
-    <comment ref="BT2" authorId="0">
+    <comment ref="BY2" authorId="0">
       <text>
         <r>
           <t>Only when Funding Source = "Central - State Share". Central % + State % must not exceed 100.</t>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="222">
   <si>
     <t>BUIDCO Input Sheet — Project Register Template</t>
   </si>
@@ -145,7 +145,7 @@
     <t>CoS/EoT events, GeoTagging photos, and Management Action items each belong to a project but are entered from the Input Sheet directly after the project exists — the "…Log" sheets here are blank reference templates for jotting that data down by hand, not something this import reads.</t>
   </si>
   <si>
-    <t>Generated: 2026-10-03 10:09:27Z</t>
+    <t>Generated: 2026-10-28 06:11:53Z</t>
   </si>
   <si>
     <t>#</t>
@@ -322,6 +322,21 @@
     <t>PBG Issuing Bank</t>
   </si>
   <si>
+    <t>Insurance Policy Number</t>
+  </si>
+  <si>
+    <t>Insurer</t>
+  </si>
+  <si>
+    <t>Insured Amount (Rs. Cr.)</t>
+  </si>
+  <si>
+    <t>Insurance Start Date</t>
+  </si>
+  <si>
+    <t>Insurance Expiry Date</t>
+  </si>
+  <si>
     <t>EMD Amount (Rs. Cr.)</t>
   </si>
   <si>
@@ -623,9 +638,6 @@
   </si>
   <si>
     <t>AMRUT 2.0</t>
-  </si>
-  <si>
-    <t>MMSSVY</t>
   </si>
   <si>
     <t>Namami Gange</t>
@@ -1412,7 +1424,7 @@
   <sheetPr>
     <tabColor rgb="FF1E3A5F"/>
   </sheetPr>
-  <dimension ref="A1:BT203"/>
+  <dimension ref="A1:BY203"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1454,28 +1466,31 @@
     <col min="47" max="48" width="18" customWidth="1"/>
     <col min="49" max="49" width="16" customWidth="1"/>
     <col min="50" max="50" width="22" customWidth="1"/>
-    <col min="51" max="51" width="18" customWidth="1"/>
-    <col min="52" max="52" width="20" customWidth="1"/>
-    <col min="53" max="53" width="16" customWidth="1"/>
-    <col min="54" max="54" width="22" customWidth="1"/>
-    <col min="55" max="55" width="16" customWidth="1"/>
-    <col min="56" max="56" width="18" customWidth="1"/>
-    <col min="57" max="57" width="34" customWidth="1"/>
-    <col min="58" max="58" width="12" customWidth="1"/>
-    <col min="59" max="59" width="34" customWidth="1"/>
-    <col min="60" max="60" width="14" customWidth="1"/>
-    <col min="61" max="61" width="16" customWidth="1"/>
-    <col min="62" max="63" width="20" customWidth="1"/>
-    <col min="64" max="64" width="24" customWidth="1"/>
-    <col min="65" max="65" width="22" customWidth="1"/>
-    <col min="66" max="66" width="30" customWidth="1"/>
-    <col min="67" max="67" width="26" customWidth="1"/>
-    <col min="68" max="69" width="20" customWidth="1"/>
+    <col min="51" max="51" width="20" customWidth="1"/>
+    <col min="52" max="52" width="22" customWidth="1"/>
+    <col min="53" max="53" width="20" customWidth="1"/>
+    <col min="54" max="56" width="18" customWidth="1"/>
+    <col min="57" max="57" width="20" customWidth="1"/>
+    <col min="58" max="58" width="16" customWidth="1"/>
+    <col min="59" max="59" width="22" customWidth="1"/>
+    <col min="60" max="60" width="16" customWidth="1"/>
+    <col min="61" max="61" width="18" customWidth="1"/>
+    <col min="62" max="62" width="34" customWidth="1"/>
+    <col min="63" max="63" width="12" customWidth="1"/>
+    <col min="64" max="64" width="34" customWidth="1"/>
+    <col min="65" max="65" width="14" customWidth="1"/>
+    <col min="66" max="66" width="16" customWidth="1"/>
+    <col min="67" max="68" width="20" customWidth="1"/>
+    <col min="69" max="69" width="24" customWidth="1"/>
     <col min="70" max="70" width="22" customWidth="1"/>
-    <col min="71" max="72" width="18" customWidth="1"/>
+    <col min="71" max="71" width="30" customWidth="1"/>
+    <col min="72" max="72" width="26" customWidth="1"/>
+    <col min="73" max="74" width="20" customWidth="1"/>
+    <col min="75" max="75" width="22" customWidth="1"/>
+    <col min="76" max="77" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>18</v>
       </c>
@@ -1644,29 +1659,29 @@
       <c r="BD1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BE1" s="10" t="s">
+      <c r="BE1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="BF1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="BG1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="BH1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="BI1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="BJ1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="BF1" s="11" t="s">
+      <c r="BK1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="BG1" s="11" t="s">
+      <c r="BL1" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="BH1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="BI1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="BJ1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="BK1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="BL1" s="12" t="s">
-        <v>25</v>
       </c>
       <c r="BM1" s="12" t="s">
         <v>25</v>
@@ -1674,26 +1689,41 @@
       <c r="BN1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="BO1" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="BP1" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="BQ1" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="BR1" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="BS1" s="13" t="s">
-        <v>26</v>
+      <c r="BO1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="BP1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="BQ1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="BR1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="BS1" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="BT1" s="13" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" ht="32" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BU1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="BV1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="BW1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="BX1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="BY1" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>18</v>
       </c>
@@ -1910,220 +1940,250 @@
       <c r="BT2" s="14" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="3" ht="14" customHeight="1" spans="2:72" x14ac:dyDescent="0.25">
+      <c r="BU2" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="BV2" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="BW2" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="BX2" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="BY2" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1" spans="2:77" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N3" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="O3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="O3" s="16" t="s">
-        <v>98</v>
-      </c>
       <c r="P3" s="16" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="R3" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="S3" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="U3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="V3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="W3" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="X3" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y3" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U3" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="V3" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="X3" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y3" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AD3" s="16" t="s">
-        <v>98</v>
-      </c>
       <c r="AE3" s="16" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AF3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AG3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AH3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AI3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AJ3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AK3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AL3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AM3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AN3" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO3" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AS3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AT3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AU3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="AO3" s="16" t="s">
+      <c r="AV3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AW3" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="AP3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AQ3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AR3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AS3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AT3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AU3" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="AV3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AW3" s="16" t="s">
+      <c r="AY3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="AX3" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="AY3" s="16" t="s">
-        <v>105</v>
-      </c>
       <c r="AZ3" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="BA3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="BB3" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="BC3" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="BE3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="BB3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="BC3" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="BD3" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE3" s="16" t="s">
-        <v>98</v>
-      </c>
       <c r="BF3" s="16" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="BG3" s="16" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="BH3" s="16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BI3" s="16" t="s">
         <v>103</v>
       </c>
       <c r="BJ3" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BK3" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="BL3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="BL3" s="16" t="s">
-        <v>98</v>
-      </c>
       <c r="BM3" s="16" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="BN3" s="16" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="BO3" s="16" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="BP3" s="16" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BQ3" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BR3" s="16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BS3" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="BT3" s="16" t="s">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="BU3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="BV3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="BW3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="BX3" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="BY3" s="16" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -3127,8 +3187,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BT2"/>
-  <dataValidations count="44">
+  <autoFilter ref="A2:BY2"/>
+  <dataValidations count="47">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="AA4:AA203">
       <formula1>0</formula1>
     </dataValidation>
@@ -3168,53 +3228,62 @@
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="AW4:AW203">
       <formula1>32874</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="AY4:AY203">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BA4:BA203">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="BA4:BA203">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="BB4:BB203">
       <formula1>32874</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BB4:BB203">
-      <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="BC4:BC203">
       <formula1>32874</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: High, Medium, Low, N/A" sqref="BF4:BF203">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BD4:BD203">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="BF4:BF203">
+      <formula1>32874</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BG4:BG203">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="BH4:BH203">
+      <formula1>32874</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: High, Medium, Low, N/A" sqref="BK4:BK203">
       <formula1>"High,Medium,Low,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick Yes or No." sqref="BH4:BH203">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick Yes or No." sqref="BM4:BM203">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="BI4:BI203">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="BN4:BN203">
       <formula1>32874</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BJ4:BJ203">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BO4:BO203">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="BK4:BK203">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a valid date (YYYY-MM-DD or use the Excel date picker)." sqref="BP4:BP203">
       <formula1>32874</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: Not Started, Ongoing, Expiring Soon, Expired, Handed Over to ULB" sqref="BM4:BM203">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: Not Started, Ongoing, Expiring Soon, Expired, Handed Over to ULB" sqref="BR4:BR203">
       <formula1>"Not Started,Ongoing,Expiring Soon,Expired,Handed Over to ULB"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: Central - EAP, Central - Non-EAP, Central - State Share, State Funded" sqref="BO4:BO203">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: Central - EAP, Central - Non-EAP, Central - State Share, State Funded" sqref="BT4:BT203">
       <formula1>"Central - EAP,Central - Non-EAP,Central - State Share,State Funded"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BP4:BP203">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BU4:BU203">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BQ4:BQ203">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BV4:BV203">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BR4:BR203">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BW4:BW203">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Invalid percentage" error="Enter a number between 0 and 100 (e.g. 42.5, not 0.425)." sqref="BS4:BS203">
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Invalid percentage" error="Enter a number between 0 and 100 (e.g. 42.5, not 0.425)." sqref="BX4:BX203">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Invalid percentage" error="Enter a number between 0 and 100 (e.g. 42.5, not 0.425)." sqref="BT4:BT203">
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Invalid percentage" error="Enter a number between 0 and 100 (e.g. 42.5, not 0.425)." sqref="BY4:BY203">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -3225,7 +3294,7 @@
       <formula1>=Divisions!$A$2:$A$46</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick a name from the Schemes sheet." sqref="H4:H203">
-      <formula1>=Schemes!$A$2:$A$9</formula1>
+      <formula1>=Schemes!$A$2:$A$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick one of: Work Contract, Service Contract, O&amp;M Contract, Others" sqref="K4:K203">
       <formula1>"Work Contract,Service Contract,O&amp;M Contract,Others"</formula1>
@@ -3287,37 +3356,37 @@
         <v>27</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L1" s="17" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -3345,13 +3414,13 @@
         <v>27</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3374,13 +3443,13 @@
         <v>27</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -3407,32 +3476,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3455,232 +3524,232 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3695,7 +3764,7 @@
   <sheetPr>
     <tabColor rgb="FF6B7280"/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -3703,51 +3772,46 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A9"/>
+  <autoFilter ref="A1:A8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3766,117 +3830,117 @@
   <sheetData>
     <row r="1" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3884,16 +3948,16 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F6" t="s">
         <v>1</v>
@@ -3907,7 +3971,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
@@ -3930,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
